--- a/Samples/Sample_Teacher_details.xlsx
+++ b/Samples/Sample_Teacher_details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikhi\OneDrive\Desktop\New folder (2)\Teachers-App\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikhi\OneDrive\Desktop\m\Teachers-App-private\Samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B411D3-436D-40CE-A7B0-796FA4C9391C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C8F378-CE3E-4B01-A4BB-13DE8BC7267E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,19 +37,19 @@
     <t>B.Tech</t>
   </si>
   <si>
-    <t>Computer Science</t>
-  </si>
-  <si>
     <t>Science</t>
   </si>
   <si>
-    <t>ABCS</t>
-  </si>
-  <si>
     <t>XYZ</t>
   </si>
   <si>
     <t>IT,AI</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Maths</t>
   </si>
 </sst>
 </file>
@@ -465,13 +465,13 @@
     </row>
     <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
